--- a/artfynd/A 34006-2023 artfynd.xlsx
+++ b/artfynd/A 34006-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 34006-2023 artfynd.xlsx
+++ b/artfynd/A 34006-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96973219</v>
+        <v>96973226</v>
       </c>
       <c r="B2" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,27 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543371.8991469519</v>
+        <v>543418</v>
       </c>
       <c r="R2" t="n">
-        <v>7099457.585369363</v>
+        <v>7099547</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -752,27 +746,18 @@
           <t>2021-10-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-10-01</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -788,6 +773,426 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>96973211</v>
+      </c>
+      <c r="B3" t="n">
+        <v>80433</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Hundberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>543456</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7099437</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Alanäs</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2021-10-01</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2021-10-01</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>96973214</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hundberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>543515</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7099439</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Alanäs</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2021-10-01</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2021-10-01</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>96973201</v>
+      </c>
+      <c r="B5" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hundberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>543507</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7099439</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Alanäs</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2021-10-01</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2021-10-01</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>96973219</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hundberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>543372</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7099457</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Alanäs</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2021-10-01</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2021-10-01</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
         </is>

--- a/artfynd/A 34006-2023 artfynd.xlsx
+++ b/artfynd/A 34006-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -777,6 +782,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96973226</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,6 +892,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96973211</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96973214</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1090,6 +1110,11 @@
       <c r="AY5" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96973201</t>
         </is>
       </c>
     </row>
@@ -1197,8 +1222,20 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96973219</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>